--- a/outputs/run-customer-validate/Legacy19TestCase.generated.xlsx
+++ b/outputs/run-customer-validate/Legacy19TestCase.generated.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Test Cases'!$A$1:$S$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Test Cases'!$A$1:$S$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,16 +43,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF3F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,24 +77,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -184,8 +168,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="APITestCases" displayName="APITestCases" ref="A1:S22" headerRowCount="1">
-  <autoFilter ref="A1:S22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="APITestCases" displayName="APITestCases" ref="A1:S30" headerRowCount="1">
+  <autoFilter ref="A1:S30"/>
   <tableColumns count="19">
     <tableColumn id="1" name="Test Case ID"/>
     <tableColumn id="2" name="Function"/>
@@ -500,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -634,47 +618,56 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Method &amp; Header</t>
+          <t>Protocol &amp; Headers</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>POST hợp lệ vi</t>
+          <t>POST hợp lệ</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: METHOD; Primary Condition: POST method accepted; Source: TD_P1_001 / API spec page 1</t>
+          <t>Primary Condition: POST method with valid headers and payload; kiểm tra gọi API thành công</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; có authToken; source API spec page 1</t>
+          <t>Kết nối mạng SIT ổn định; Token xác thực còn hiệu lực</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: METHOD
-Primary Condition: POST method accepted
-Source: TD_P1_001 / API spec page 1
-Headers: authToken=test_token, requestID=REQ-001, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"123456789012"}</t>
+          <t>Headers:
+- authToken: "ValidToken_QA_2026"
+- requestID: "REQ-20260520-001"
+- X-App-Code: "CCTG_ONLINE_PORTAL"
+- Accept-language: "vi"
+- Content-Type: "application/json"
+Body:
+{
+  "requestCif": "685607800001"
+}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Thiết lập đầy đủ headers bắt buộc
-3. Gửi request với body chứa requestCif gồm 12 chữ số
-4. Kiểm tra HTTP status và response envelope</t>
+          <t>1. Thiết lập phương thức POST và endpoint /v1/customer/validate
+2. Cấu hình đầy đủ headers theo danh sách dữ liệu test
+3. Đính kèm request body chứa requestCif gồm 12 chữ số hợp lệ nghiệp vụ
+4. Thực hiện gửi request và kiểm tra phản hồi từ hệ thống</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>HTTP Status: 200
-Kiểm tra response có code, message, success, errors, traceId, responseTime
-Kiểm tra code="0", message="SUCCESS", success=true, errors=null
-Kiểm tra không phát sinh HTTP 500</t>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 200 OK
+Verify response JSON có cấu trúc thành công:
+- success: true
+- code: "0"
+- message: "SUCCESS"
+- errors: null
+- traceId: chuỗi định dạng UUID không rỗng
+- responseTime: thời gian ISO-8601 hợp lệ</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -702,12 +695,16 @@
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: RESPONSE_SCHEMA</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="120" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TD_P1_001_TC_002</t>
+          <t>TD_P1_002_TC_001</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -717,46 +714,42 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Method &amp; Header</t>
+          <t>Protocol &amp; Headers</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>POST hợp lệ en</t>
+          <t>GET không hỗ trợ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Coverage: LANGUAGE; Primary Condition: Accept-language en accepted; Source: TD_P1_007 / API spec page 1</t>
+          <t>Primary Condition: Gửi request với HTTP method GET không hợp lệ</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; có authToken; source API spec page 1</t>
+          <t>Endpoint /v1/customer/validate được cấu hình trên Gateway</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Coverage: LANGUAGE
-Primary Condition: Accept-language en accepted
-Source: TD_P1_007 / API spec page 1
-Headers: authToken=test_token, requestID=REQ-002, X-App-Code=NMS, Accept-language=en, Content-Type=application/json
-Body: {"requestCif":"123456789012"}</t>
+          <t>Headers &amp; Body như TD_P1_001 nhưng đổi Method sang GET</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Thiết lập header Accept-language=en
-3. Gửi request với body chứa requestCif gồm 12 chữ số
-4. Kiểm tra response trả về theo ngôn ngữ tiếng Anh</t>
+          <t>1. Thiết lập phương thức GET và endpoint /v1/customer/validate
+2. Gửi request kèm đầy đủ headers và body
+3. Thực hiện gửi request và kiểm tra phản hồi lỗi</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>HTTP Status: 200
-Kiểm tra response có code, message, success, errors, traceId, responseTime
-Kiểm tra code="0", message="SUCCESS", success=true</t>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 405 Method Not Allowed hoặc HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: mã lỗi phương thức hoặc thông báo lỗi từ Gateway</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -766,7 +759,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -784,12 +777,16 @@
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: METHOD</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TD_P1_002_TC_001</t>
+          <t>TD_P1_003_TC_001</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -799,46 +796,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Method &amp; Header</t>
+          <t>Protocol &amp; Headers</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>GET không hỗ trợ</t>
+          <t>Content-Type không hợp lệ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Coverage: METHOD; Primary Condition: GET method rejected; Source: [ASSUMPTION: tester-standard gateway/API behavior]</t>
+          <t>Primary Condition: Gửi request với Content-Type không hợp lệ</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; có authToken; source API spec page 1</t>
+          <t>Hệ thống kiểm tra định dạng gói tin đầu vào</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Coverage: METHOD
-Primary Condition: GET method rejected
-Source: [ASSUMPTION: tester-standard gateway/API behavior]
-Headers: authToken=test_token, requestID=REQ-003, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"123456789012"}</t>
+          <t>Header Content-Type: "text/plain"
+Body: "{ \"requestCif\": \"685607800001\" }"</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1. Thiết lập method GET và endpoint /v1/customer/validate
-2. Thiết lập đầy đủ headers bắt buộc
-3. Gửi request với body chứa requestCif gồm 12 chữ số
-4. Kiểm tra response báo lỗi phương thức không được hỗ trợ</t>
+          <t>1. Thiết lập phương thức POST và endpoint /v1/customer/validate
+2. Cấu hình header Content-Type là "text/plain"
+3. Gửi request chứa body dạng text thô
+4. Thực hiện gửi request và kiểm tra phản hồi lỗi</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>HTTP Status: 405 hoặc gateway validation status theo đặc tả
-Kiểm tra response có code hoặc message mô tả phương thức không được hỗ trợ
-Kiểm tra success=false</t>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 415 Unsupported Media Type hoặc HTTP Status: 400 Bad Request
+Response:
+- success: false
+- Có mã lỗi hoặc thông báo định dạng không hợp lệ</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -866,12 +861,16 @@
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: CONTENT_TYPE</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="120" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TD_P1_001_TC_003</t>
+          <t>TD_P1_004_TC_001</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -881,46 +880,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Method &amp; Header</t>
+          <t>Protocol &amp; Headers</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Content-Type không hỗ trợ</t>
+          <t>Thiếu header authToken</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Coverage: CONTENT_TYPE; Primary Condition: text plain Content-Type rejected; Source: [ASSUMPTION: tester-standard gateway/API behavior]</t>
+          <t>Primary Condition: Thiếu header authToken bắt buộc xác thực</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; có authToken; source API spec page 1</t>
+          <t>Khách hàng chưa đăng nhập hoặc session hết hạn</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Coverage: CONTENT_TYPE
-Primary Condition: text plain Content-Type rejected
-Source: [ASSUMPTION: tester-standard gateway/API behavior]
-Headers: authToken=test_token, requestID=REQ-004, X-App-Code=NMS, Accept-language=vi, Content-Type=text/plain
-Body: {"requestCif":"123456789012"}</t>
+          <t>Headers không chứa key authToken
+Các thông tin khác hợp lệ</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Thiết lập header Content-Type=text/plain
-3. Gửi request với body JSON chứa requestCif gồm 12 chữ số
-4. Kiểm tra response báo lỗi kiểu nội dung không hợp lệ</t>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Loại bỏ header authToken khỏi request headers
+3. Gửi request với body hợp lệ
+4. Thực hiện gửi request và kiểm tra lỗi xác thực</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>HTTP Status: 415 hoặc validation status theo đặc tả
-Kiểm tra response có code hoặc message mô tả Content-Type không được hỗ trợ
-Kiểm tra success=false</t>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 401 Unauthorized hoặc HTTP Status: 400 Bad Request
+Response:
+- success: false
+- Báo lỗi xác thực thông tin tài khoản</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -930,7 +927,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,12 +945,16 @@
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: AUTH</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TD_P1_003_TC_001</t>
+          <t>TD_P1_005_TC_001</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -963,46 +964,43 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Method &amp; Header</t>
+          <t>Protocol &amp; Headers</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Thiếu authToken</t>
+          <t>Thiếu header requestID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Coverage: AUTH; Primary Condition: authToken header missing; Source: TD_P1_003 / API spec page 1</t>
+          <t>Primary Condition: Thiếu header requestID bắt buộc kiểm tra</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; bỏ header authToken; source API spec page 1</t>
+          <t>Cấu hình tham số bắt buộc của API Gateway</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Coverage: AUTH
-Primary Condition: authToken header missing
-Source: TD_P1_003 / API spec page 1
-Headers: requestID=REQ-005, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"123456789012"}</t>
+          <t>Headers không chứa key requestID
+Các thông tin khác hợp lệ</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Bỏ header authToken khỏi request
-3. Gửi request với body chứa requestCif gồm 12 chữ số
-4. Kiểm tra response báo lỗi không có quyền truy cập</t>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Loại bỏ header requestID khỏi request headers
+3. Gửi request và kiểm tra lỗi</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>HTTP Status: 401 hoặc authentication status theo đặc tả
-Kiểm tra response có code hoặc message mô tả thiếu authToken
-Kiểm tra success=false</t>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- Báo thiếu trường bắt buộc hoặc thiếu requestID</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1030,12 +1028,16 @@
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: MANDATORY_HEADERS</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TD_P1_004_TC_001</t>
+          <t>TD_P1_006_TC_001</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1045,46 +1047,43 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Method &amp; Header</t>
+          <t>Protocol &amp; Headers</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Thiếu requestID</t>
+          <t>Thiếu header X-App-Code</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Coverage: MANDATORY_HEADERS; Primary Condition: requestID header missing; Source: TD_P1_004 / API spec page 1</t>
+          <t>Primary Condition: Thiếu header X-App-Code bắt buộc kiểm tra</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; bỏ header requestID; source API spec page 1</t>
+          <t>Cấu hình nhận diện ứng dụng gọi API</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Coverage: MANDATORY_HEADERS
-Primary Condition: requestID header missing
-Source: TD_P1_004 / API spec page 1
-Headers: authToken=test_token, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"123456789012"}</t>
+          <t>Headers không chứa key X-App-Code
+Các thông tin khác hợp lệ</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Bỏ header requestID khỏi request
-3. Gửi request với body chứa requestCif gồm 12 chữ số
-4. Kiểm tra response báo lỗi thiếu thông tin bắt buộc</t>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Loại bỏ header X-App-Code khỏi request headers
+3. Gửi request và kiểm tra lỗi</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>HTTP Status: 400 hoặc validation status theo đặc tả
-Kiểm tra response có code hoặc message mô tả thiếu requestID
-Kiểm tra success=false</t>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- Báo thiếu thông tin định danh ứng dụng gọi API</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,12 +1111,16 @@
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: MANDATORY_HEADERS</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="120" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TD_P1_004_TC_002</t>
+          <t>TD_P1_007_TC_001</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1127,46 +1130,40 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Method &amp; Header</t>
+          <t>Protocol &amp; Headers</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Thiếu X-App-Code</t>
+          <t>Thiếu header Accept-language</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Coverage: MANDATORY_HEADERS; Primary Condition: X-App-Code header missing; Source: TD_P1_005 / API spec page 1</t>
+          <t>Primary Condition: Thiếu header Accept-language trong yêu cầu</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; bỏ header X-App-Code; source API spec page 1</t>
+          <t>Hệ thống sử dụng ngôn ngữ mặc định</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Coverage: MANDATORY_HEADERS
-Primary Condition: X-App-Code header missing
-Source: TD_P1_005 / API spec page 1
-Headers: authToken=test_token, requestID=REQ-006, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"123456789012"}</t>
+          <t>Headers không chứa key Accept-language
+Các thông tin khác hợp lệ</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Bỏ header X-App-Code khỏi request
-3. Gửi request với body chứa requestCif gồm 12 chữ số
-4. Kiểm tra response báo lỗi thiếu app code</t>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Loại bỏ header Accept-language khỏi request headers
+3. Gửi request và kiểm tra ngôn ngữ trả về</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>HTTP Status: 400 hoặc validation status theo đặc tả
-Kiểm tra response có code hoặc message mô tả thiếu X-App-Code
-Kiểm tra success=false</t>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 200 OK (nếu fallback về ngôn ngữ mặc định là vi) hoặc HTTP Status: 400 Bad Request. Phản hồi response có ngôn ngữ mặc định.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1176,7 +1173,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1194,12 +1191,16 @@
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: LANGUAGE</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="120" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TD_P1_004_TC_003</t>
+          <t>TD_P1_008_TC_001</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1209,46 +1210,40 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Method &amp; Header</t>
+          <t>Protocol &amp; Headers</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Thiếu Accept-language</t>
+          <t>Accept-language không hỗ trợ</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Coverage: MANDATORY_HEADERS; Primary Condition: Accept-language header missing; Source: TD_P1_001 / API spec page 1</t>
+          <t>Primary Condition: Header Accept-language sai giá trị không được hỗ trợ</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; bỏ header Accept-language; source API spec page 1</t>
+          <t>Hệ thống hỗ trợ xử lý đa ngôn ngữ</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Coverage: MANDATORY_HEADERS
-Primary Condition: Accept-language header missing
-Source: TD_P1_001 / API spec page 1
-Headers: authToken=test_token, requestID=REQ-007, X-App-Code=NMS, Content-Type=application/json
-Body: {"requestCif":"123456789012"}</t>
+          <t>Header Accept-language: "fr"
+Các thông tin khác hợp lệ</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Bỏ header Accept-language khỏi request
-3. Gửi request với body chứa requestCif gồm 12 chữ số
-4. Kiểm tra response báo lỗi thiếu ngôn ngữ</t>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Cấu hình header Accept-language là "fr"
+3. Gửi request và kiểm tra lỗi</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>HTTP Status: 400 hoặc validation status theo đặc tả
-Kiểm tra response có code hoặc message mô tả thiếu Accept-language
-Kiểm tra success=false</t>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request hoặc tự động sử dụng ngôn ngữ mặc định. Báo lỗi hoặc response trả về an toàn.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1258,7 +1253,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1276,12 +1271,16 @@
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: LANGUAGE</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TD_P1_006_TC_001</t>
+          <t>TD_P2_001_TC_001</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1291,46 +1290,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Method &amp; Header</t>
+          <t>Body Schema Validation</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Accept-Language tiếng Việt</t>
+          <t>Thiếu trường requestCif</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Coverage: LANGUAGE; Primary Condition: Accept-language vi accepted; Source: TD_P1_006 / API spec page 1</t>
+          <t>Primary Condition: Thiếu trường requestCif trong body payload</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; Accept-Language=vi; source API spec page 1</t>
+          <t>Ràng buộc schema gói tin request</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Coverage: LANGUAGE
-Primary Condition: Accept-language vi accepted
-Source: TD_P1_006 / API spec page 1
-Headers: authToken=test_token, requestID=REQ-008, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"123456789012"}</t>
+          <t>Body:
+{
+}</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Thiết lập header Accept-language=vi
-3. Gửi request với body chứa requestCif gồm 12 chữ số
-4. Kiểm tra response trả về theo ngôn ngữ tiếng Việt</t>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Cấu hình request body rỗng {}
+3. Gửi request và kiểm tra thông tin lỗi</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>HTTP Status: 200
-Kiểm tra response có code, message, success, errors, traceId, responseTime
-Kiểm tra code="0", message="SUCCESS", success=true</t>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Verify response JSON có cấu trúc failure:
+- success: false
+- Báo lỗi thiếu trường bắt buộc requestCif</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1340,7 +1337,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1358,900 +1355,956 @@
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: RESPONSE_SCHEMA</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>TD_P2_001_TC_001</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TD_P2_002_TC_001</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>POST /v1/customer/validate</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Schema Validation</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Thiếu requestCif</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: BODY_SCHEMA; Primary Condition: requestCif field missing; Source: TD_P2_001 / API spec page 1</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; headers hợp lệ; source API spec page 1</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: BODY_SCHEMA
-Primary Condition: requestCif field missing
-Source: TD_P2_001 / API spec page 1
-Headers: authToken=test_token, requestID=REQ-009, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {}</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Thiết lập headers đầy đủ
-3. Gửi request với body rỗng không có key requestCif
-4. Kiểm tra validation response cho trường requestCif</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>HTTP Status: 400 hoặc validation status theo đặc tả
-Kiểm tra success=false
-Kiểm tra code hoặc message mô tả thiếu requestCif</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Body Schema Validation</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Sai kiểu dữ liệu requestCif</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Primary Condition: Trường requestCif truyền sai kiểu dữ liệu kiểu số thay vì chuỗi</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Ràng buộc schema kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": 685607800001
+}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Cấu hình request body chứa requestCif là số 685607800001
+3. Gửi request và kiểm tra lỗi</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- Báo lỗi sai định dạng hoặc kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>SIT</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: BODY_SCHEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TD_P2_003_TC_001</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Body Schema Validation</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>requestCif rỗng</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Primary Condition: Trường requestCif rỗng không hợp lệ</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Ràng buộc schema kiểm tra độ dài tối thiểu</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": ""
+}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Cấu hình request body có requestCif = ""
+3. Gửi request và kiểm tra lỗi</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- Báo lỗi trường bắt buộc không được để trống</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: BODY_SCHEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TD_P2_004_TC_001</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Body Schema Validation</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>requestCif ngắn hơn 12 ký tự</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Primary Condition: Độ dài trường requestCif ngắn hơn quy định biên dưới</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Ràng buộc schema kiểm tra độ dài biên dưới</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "12345678901"
+}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Cấu hình request body có requestCif dài 11 chữ số
+3. Gửi request và kiểm tra lỗi</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- Báo lỗi độ dài CIF không hợp lệ</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TD_P2_005_TC_001</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Body Schema Validation</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>requestCif dài hơn 12 ký tự</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Primary Condition: Độ dài trường requestCif dài hơn quy định biên trên</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Ràng buộc schema kiểm tra độ dài biên trên</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "1234567890123"
+}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Cấu hình request body có requestCif dài 13 chữ số
+3. Gửi request và kiểm tra lỗi</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- Báo lỗi độ dài CIF không hợp lệ</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TD_P2_006_TC_001</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Body Schema Validation</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>requestCif chứa chữ</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Primary Condition: Định dạng trường requestCif chứa chữ cái không hợp lệ</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Kiểm tra ký tự chữ cái trong CIF</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "12345678901a"
+}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Cấu hình request body có requestCif chứa ký tự chữ cái 'a'
+3. Gửi request và kiểm tra lỗi</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- Báo lỗi định dạng CIF không hợp lệ</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: BODY_SCHEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TD_P2_006_TC_002</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Body Schema Validation</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>requestCif chứa ký tự đặc biệt</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Primary Condition: Định dạng trường requestCif chứa ký tự đặc biệt không hợp lệ</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Kiểm tra ký tự đặc biệt trong CIF</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "12345678901#"
+}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1. Thiết lập request POST /v1/customer/validate
+2. Cấu hình request body có requestCif chứa ký tự '#'
+3. Gửi request và kiểm tra lỗi</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- Báo lỗi định dạng CIF không hợp lệ</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: BODY_SCHEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_001_TC_001</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Lỗi quốc tịch 101</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Field quốc tịch của khách hàng không hợp lệ</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Khách hàng tồn tại trên Core, quốc tịch không phải Việt Nam (ví dụ: US)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "101101101101"
+}</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>1. Chuẩn bị khách hàng có quốc tịch nước ngoài trên Core Banking
+2. Gửi request POST /v1/customer/validate với requestCif của khách hàng
+3. Thực hiện gửi request và kiểm tra phản hồi lỗi</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: "101"
+- message: "quốc tịch không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>TD_P2_002_TC_001</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: BUSINESS_ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_002_TC_001</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>POST /v1/customer/validate</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Schema Validation</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>requestCif ngắn hơn 12 ký tự</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: BOUNDARY; Primary Condition: requestCif length check; Source: TD_P2_002 / API spec page 1</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; headers hợp lệ; source API spec page 1</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: BOUNDARY
-Primary Condition: requestCif length check
-Source: TD_P2_002 / API spec page 1
-Headers: authToken=test_token, requestID=REQ-010, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"12345678901"}</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Thiết lập headers đầy đủ
-3. Gửi request với body chứa requestCif dài 11 ký tự
-4. Kiểm tra validation response cho độ dài trường requestCif</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>HTTP Status: 400 hoặc validation status theo đặc tả
-Kiểm tra success=false
-Kiểm tra code hoặc message mô tả requestCif không đúng độ dài</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Lỗi tuổi 102</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Field tuổi của khách hàng không hợp lệ</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Khách hàng tồn tại trên Core, ngày sinh khiến tuổi tròn là 17</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "102102102102"
+}</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>1. Chuẩn bị khách hàng 17 tuổi trên Core Banking
+2. Gửi request POST /v1/customer/validate với requestCif của khách hàng
+3. Thực hiện gửi request và kiểm tra phản hồi lỗi</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: "102"
+- message: "tuổi không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>SIT</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>TD_P2_002_TC_002</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: BUSINESS_ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_003_TC_001</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>POST /v1/customer/validate</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Schema Validation</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>requestCif dài hơn 12 ký tự</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: BOUNDARY; Primary Condition: requestCif length check; Source: TD_P2_003 / API spec page 1</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; headers hợp lệ; source API spec page 1</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: BOUNDARY
-Primary Condition: requestCif length check
-Source: TD_P2_003 / API spec page 1
-Headers: authToken=test_token, requestID=REQ-011, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"1234567890123"}</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Thiết lập headers đầy đủ
-3. Gửi request với body chứa requestCif dài 13 ký tự
-4. Kiểm tra validation response cho độ dài trường requestCif</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>HTTP Status: 400 hoặc validation status theo đặc tả
-Kiểm tra success=false
-Kiểm tra code hoặc message mô tả requestCif không đúng độ dài</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Khách hàng 18 tuổi</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Khách hàng hợp lệ vừa tròn 18 tuổi</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Khách hàng tồn tại trên Core, ngày sinh khiến tuổi tròn đúng 18</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "102181021800"
+}</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>1. Chuẩn bị khách hàng vừa tròn đúng 18 tuổi trên Core Banking
+2. Gửi request POST /v1/customer/validate với requestCif của khách hàng
+3. Thực hiện gửi request và kiểm tra phản hồi</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 200 OK
+Response:
+- success: true
+- code: "0"
+- message: "SUCCESS"</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>SIT</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>TD_P2_004_TC_001</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: RESPONSE_SCHEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_004_TC_001</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>POST /v1/customer/validate</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Schema Validation</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>requestCif sai kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: BODY_SCHEMA; Primary Condition: requestCif type is invalid; Source: TD_P2_004 / API spec page 1</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; headers hợp lệ; source API spec page 1</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: BODY_SCHEMA
-Primary Condition: requestCif type is invalid
-Source: TD_P2_004 / API spec page 1
-Headers: authToken=test_token, requestID=REQ-012, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":123456789012}</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Thiết lập headers đầy đủ
-3. Gửi request với body chứa requestCif có giá trị là số 123456789012 không có dấu nháy kép
-4. Kiểm tra validation response cho trường requestCif</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>HTTP Status: 400 hoặc validation status theo đặc tả
-Kiểm tra success=false
-Kiểm tra code hoặc message mô tả requestCif sai định dạng hoặc sai kiểu dữ liệu</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Lỗi loại khách hàng 103</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Field loại khách hàng doanh nghiệp không hợp lệ</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Khách hàng tồn tại trên Core, thuộc nhóm doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "103103103103"
+}</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>1. Chuẩn bị thông tin khách hàng tổ chức trên Core Banking
+2. Gửi request POST /v1/customer/validate với requestCif
+3. Thực hiện gửi request và kiểm tra phản hồi lỗi</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: "103"
+- message: "loại khách hàng không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>SIT</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15" ht="120" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>TD_P2_005_TC_001</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: BUSINESS_ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_005_TC_001</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>POST /v1/customer/validate</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Schema Validation</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Cấu trúc response thành công</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: RESPONSE_SCHEMA; Primary Condition: success response schema check; Source: TD_P2_005 / API response schema</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; headers hợp lệ; source API response schema</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: RESPONSE_SCHEMA
-Primary Condition: success response schema check
-Source: TD_P2_005 / API response schema
-Headers: authToken=test_token, requestID=REQ-013, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"123456789012"}</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Gửi request với body chứa requestCif dài 12 ký tự
-3. Kiểm tra cấu trúc schema response thành công</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>HTTP Status: 200
-Kiểm tra response body có success=true, code="0", message="SUCCESS", errors=null, traceId (dạng string), responseTime (dạng datetime)</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Lỗi tình trạng cư trú 104</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Field tình trạng cư trú của khách hàng không hợp lệ</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Khách hàng tồn tại trên Core, có cờ cư trú là Không cư trú</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "104104104104"
+}</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>1. Chuẩn bị khách hàng Không cư trú trên Core Banking
+2. Gửi request POST /v1/customer/validate với requestCif
+3. Thực hiện gửi request và kiểm tra phản hồi lỗi</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: "104"
+- message: "tình trạng cư trú không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>SIT</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>TD_P2_006_TC_001</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>POST /v1/customer/validate</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Schema Validation</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Cấu trúc response thất bại</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: RESPONSE_SCHEMA; Primary Condition: failure response schema check; Source: TD_P2_006 / API response envelope</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; headers hợp lệ; source API response schema</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: RESPONSE_SCHEMA
-Primary Condition: failure response schema check
-Source: TD_P2_006 / API response envelope
-Headers: authToken=test_token, requestID=REQ-014, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"101101101101"}</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Gửi request với body chứa requestCif gây lỗi nghiệp vụ
-3. Kiểm tra cấu trúc schema response thất bại</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>HTTP Status: 400
-Kiểm tra response body có success=false, code không phải "0", message khác rỗng, errors (array hoặc null), traceId, responseTime</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>SIT</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>TD_P3_001_TC_001</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>POST /v1/customer/validate</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Value, Business Logic, Cross Logic</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Lỗi quốc tịch 101</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Coverage: BUSINESS_ERROR; Primary Condition: citizenship check code 101 rule; Source: TD_P3_001 / API spec page 2</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; headers hợp lệ; source API spec page 2</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Coverage: BUSINESS_ERROR
-Primary Condition: citizenship check code 101 rule
-Source: TD_P3_001 / API spec page 2
-Headers: authToken=test_token, requestID=REQ-015, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"101101101101"}</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị requestCif của khách hàng có quốc tịch nước ngoài
-2. Gửi POST /v1/customer/validate với body đã chuẩn bị
-3. Kiểm tra mã lỗi và thông báo lỗi quốc tịch trong response</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Status: 400
-Kiểm tra success=false, code="101", message="quốc tịch không hợp lệ"</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>SIT</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="inlineStr"/>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="120" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>TD_P3_002_TC_001</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>POST /v1/customer/validate</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Value, Business Logic, Cross Logic</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Lỗi tuổi 102</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Coverage: BUSINESS_ERROR; Primary Condition: age check code 102 rule; Source: TD_P3_002 / API spec page 2</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; headers hợp lệ; source API spec page 2</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Coverage: BUSINESS_ERROR
-Primary Condition: age check code 102 rule
-Source: TD_P3_002 / API spec page 2
-Headers: authToken=test_token, requestID=REQ-016, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"102102102102"}</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị requestCif của khách hàng có tuổi không hợp lệ (dưới 18 tuổi)
-2. Gửi POST /v1/customer/validate với body đã chuẩn bị
-3. Kiểm tra mã lỗi và thông báo lỗi tuổi trong response</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Status: 400
-Kiểm tra success=false, code="102", message="tuổi không hợp lệ"</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>SIT</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="4" t="inlineStr"/>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19" ht="120" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>TD_P3_003_TC_001</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>POST /v1/customer/validate</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Value, Business Logic, Cross Logic</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Lỗi loại khách hàng 103</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Coverage: BUSINESS_ERROR; Primary Condition: customer type check code 103 rule; Source: TD_P3_003 / API spec page 2</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; headers hợp lệ; source API spec page 2</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Coverage: BUSINESS_ERROR
-Primary Condition: customer type check code 103 rule
-Source: TD_P3_003 / API spec page 2
-Headers: authToken=test_token, requestID=REQ-017, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"103103103103"}</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị requestCif của khách hàng có loại khách hàng không hợp lệ (ví dụ: khách hàng định chế tài chính)
-2. Gửi POST /v1/customer/validate với body đã chuẩn bị
-3. Kiểm tra mã lỗi và thông báo lỗi loại khách hàng trong response</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Status: 400
-Kiểm tra success=false, code="103", message="loại khách hàng không hợp lệ"</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>SIT</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="120" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>TD_P3_004_TC_001</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>POST /v1/customer/validate</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Value, Business Logic, Cross Logic</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Lỗi tình trạng cư trú 104</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Coverage: BUSINESS_ERROR; Primary Condition: residency check code 104 rule; Source: TD_P3_004 / API spec page 3</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; headers hợp lệ; source API spec page 3</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Coverage: BUSINESS_ERROR
-Primary Condition: residency check code 104 rule
-Source: TD_P3_004 / API spec page 3
-Headers: authToken=test_token, requestID=REQ-018, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"104104104104"}</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị requestCif của khách hàng có tình trạng cư trú không hợp lệ (không cư trú)
-2. Gửi POST /v1/customer/validate với body đã chuẩn bị
-3. Kiểm tra mã lỗi và thông báo lỗi tình trạng cư trú trong response</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Status: 400
-Kiểm tra success=false, code="104", message="tình trạng cư trú không hợp lệ"</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>SIT</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21" ht="120" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>TD_P3_005_TC_001</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>POST /v1/customer/validate</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Value, Business Logic, Cross Logic</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Lỗi ngoài giờ COT 109</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Coverage: BUSINESS_ERROR; Primary Condition: cut-off time check code 109 rule; Source: TD_P3_005 / API spec page 3</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; headers hợp lệ; source API spec page 3</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Coverage: BUSINESS_ERROR
-Primary Condition: cut-off time check code 109 rule
-Source: TD_P3_005 / API spec page 3
-Headers: authToken=test_token, requestID=REQ-019, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {"requestCif":"123456789012"}</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>1. Thiết lập request gửi ngoài giờ giao dịch cho phép (Cut-Off Time)
-2. Gửi POST /v1/customer/validate với body có requestCif hợp lệ
-3. Kiểm tra mã lỗi và thông báo lỗi COT 109 trong response</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Status: 400
-Kiểm tra success=false, code="109", message="Hiện tại đã hết giờ giao dịch. Quý khách vui lòng thực hiện từ {0} đến {1} hàng ngày."</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>SIT</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr"/>
-      <c r="O21" s="4" t="inlineStr"/>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: BUSINESS_ERROR</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="120" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>TD_P2_001_TC_002</t>
+          <t>TD_P3_006_TC_001</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2261,45 +2314,46 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Schema Validation</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Đô ưu tiên lỗi</t>
+          <t>Ngoài giờ COT 109</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Coverage: ERROR_PRIORITY; Primary Condition: error priority rule; Source: [ASSUMPTION: tester-standard gateway/API behavior]</t>
+          <t>Primary Condition: Rule giờ giao dịch COT không hợp lệ</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Env SIT; Endpoint /v1/customer/validate; bỏ header requestID; body thiếu requestCif</t>
+          <t>Hệ thống đang cấu hình ngoài khung giờ hoạt động COT (ví dụ: 23:00)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Coverage: ERROR_PRIORITY
-Primary Condition: error priority rule
-Source: [ASSUMPTION: tester-standard gateway/API behavior]
-Headers: authToken=test_token, X-App-Code=NMS, Accept-language=vi, Content-Type=application/json
-Body: {}</t>
+          <t>Body:
+{
+  "requestCif": "685607800001"
+}</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>1. Thiết lập method POST và endpoint /v1/customer/validate
-2. Bỏ header requestID khỏi request
-3. Gửi request với body rỗng {}
-4. Kiểm tra lỗi nào được trả về trước trong response</t>
+          <t>1. Giả lập hoặc cấu hình giờ hệ thống nằm ngoài khung giờ COT cho phép
+2. Gửi request POST /v1/customer/validate với requestCif hợp lệ
+3. Thực hiện gửi request và kiểm tra phản hồi lỗi</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>HTTP Status: 400
-Kiểm tra response báo lỗi thiếu requestID hoặc thiếu requestCif theo thứ tự ưu tiên nhất quán</t>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: "109"
+- message: "Hiện tại đã hết giờ giao dịch. Quý khách vui lòng thực hiện từ {0} đến {1} hàng ngày."</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2309,7 +2363,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2327,18 +2381,706 @@
       <c r="P22" s="3" t="inlineStr"/>
       <c r="Q22" s="3" t="inlineStr"/>
       <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: BUSINESS_ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="120" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_007_TC_001</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Biên COT: Giao dịch lúc 07:59</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Rule biên giờ COT lúc 07:59 trước giờ mở cửa không hợp lệ</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Giờ COT cho phép từ 08:00 đến 17:00; Giờ hệ thống đang là 07:59</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "685607800001"
+}</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>1. Cấu hình giờ hệ thống là 07:59 sáng
+2. Gửi request POST /v1/customer/validate và kiểm tra phản hồi lỗi</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: "109"
+- message: "Hiện tại đã hết giờ giao dịch. Quý khách vui lòng thực hiện từ {0} đến {1} hàng ngày."</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="120" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_008_TC_001</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Biên COT: Giao dịch lúc 08:00</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Biên giờ COT lúc 08:00 đúng giờ mở cửa hợp lệ</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Giờ COT cho phép từ 08:00 đến 17:00; Giờ hệ thống đang là 08:00</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "685607800001"
+}</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>1. Cấu hình giờ hệ thống đúng 08:00 sáng
+2. Gửi request POST /v1/customer/validate và kiểm tra phản hồi</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 200 OK
+Response:
+- success: true
+- code: "0"
+- message: "SUCCESS"</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: RESPONSE_SCHEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_009_TC_001</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Biên COT: Giao dịch lúc 17:00</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Biên giờ COT lúc 17:00 đúng giờ đóng cửa hợp lệ</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Giờ COT cho phép từ 08:00 đến 17:00; Giờ hệ thống đang là 17:00</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "685607800001"
+}</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>1. Cấu hình giờ hệ thống đúng 17:00 chiều
+2. Gửi request POST /v1/customer/validate và kiểm tra phản hồi</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 200 OK
+Response:
+- success: true
+- code: "0"
+- message: "SUCCESS"</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: RESPONSE_SCHEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="120" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_010_TC_001</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Biên COT: Giao dịch lúc 17:01</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Rule biên giờ COT lúc 17:01 sau giờ đóng cửa không hợp lệ</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Giờ COT cho phép từ 08:00 đến 17:00; Giờ hệ thống đang là 17:01</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "685607800001"
+}</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>1. Cấu hình giờ hệ thống là 17:01 chiều
+2. Gửi request POST /v1/customer/validate và kiểm tra phản hồi lỗi</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: "109"
+- message: "Hiện tại đã hết giờ giao dịch. Quý khách vui lòng thực hiện từ {0} đến {1} hàng ngày."</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: BOUNDARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="120" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_011_TC_001</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Độ ưu tiên lỗi: 101 và 102</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Độ ưu tiên kiểm tra lỗi quốc tịch và tuổi</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Khách hàng có quốc tịch nước ngoài VÀ tuổi tròn là 16 tuổi</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "101102000001"
+}</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>1. Chuẩn bị khách hàng nước ngoài và 16 tuổi trên Core Banking
+2. Gửi request POST /v1/customer/validate
+3. Thực hiện gửi request và kiểm tra mã lỗi trả về có đúng độ ưu tiên lỗi</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: "101"
+- message: "quốc tịch không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: ERROR_PRIORITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="120" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_012_TC_001</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Độ ưu tiên lỗi: 102 và 103</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Độ ưu tiên kiểm tra lỗi tuổi và loại khách hàng</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Khách hàng 16 tuổi VÀ thuộc nhóm doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "102103000001"
+}</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>1. Chuẩn bị khách hàng doanh nghiệp và 16 tuổi trên Core Banking
+2. Gửi request POST /v1/customer/validate
+3. Thực hiện gửi request và kiểm tra mã lỗi trả về có đúng độ ưu tiên lỗi</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: "102"
+- message: "tuổi không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: ERROR_PRIORITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="120" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_013_TC_001</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Độ ưu tiên lỗi: 103 và 104</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Độ ưu tiên kiểm tra lỗi loại khách hàng và cư trú</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp VÀ có cờ Không cư trú</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "103104000001"
+}</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>1. Chuẩn bị khách hàng doanh nghiệp và Không cư trú trên Core Banking
+2. Gửi request POST /v1/customer/validate
+3. Thực hiện gửi request và kiểm tra mã lỗi trả về có đúng độ ưu tiên lỗi</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: "103"
+- message: "loại khách hàng không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: ERROR_PRIORITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="120" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TD_P3_014_TC_001</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>POST /v1/customer/validate</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Độ ưu tiên lỗi: 104 và 109</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Primary Condition: Độ ưu tiên kiểm tra lỗi cư trú và ngoài giờ COT</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Khách hàng Không cư trú VÀ giờ hệ thống đang là 23:00</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Body:
+{
+  "requestCif": "104109000001"
+}</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>1. Cấu hình giờ hệ thống là 23:00 đêm
+2. Gửi request POST /v1/customer/validate cho khách hàng Không cư trú
+3. Thực hiện gửi request và kiểm tra mã lỗi trả về có đúng độ ưu tiên lỗi</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra phản hồi trả về HTTP Status: 400 Bad Request
+Response:
+- success: false
+- code: "104"
+- message: "tình trạng cư trú không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t>Coverage: ERROR_PRIORITY</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S22"/>
+  <autoFilter ref="A1:S30"/>
   <dataValidations count="3">
-    <dataValidation sqref="N2:N22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,BLOCKED,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,BLOCKED,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,BLOCKED,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2363,72 +3105,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Total test cases</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>21</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Method &amp; Header</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Body Schema Validation</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Schema Validation</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Value, Business Logic, Cross Logic</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Protocol &amp; Headers</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Format note</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Escaped TSV newlines are rendered as real Excel line breaks in manual-step cells.</t>
         </is>
